--- a/static/file/PlayerUploadFormat.xlsx
+++ b/static/file/PlayerUploadFormat.xlsx
@@ -91,7 +91,7 @@
     <t xml:space="preserve">Batter</t>
   </si>
   <si>
-    <t xml:space="preserve">Vinotha</t>
+    <t xml:space="preserve">Sriarm</t>
   </si>
 </sst>
 </file>
@@ -194,15 +194,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
